--- a/survey_templates/016_market_research_questionnaire--survey_templates.xlsx
+++ b/survey_templates/016_market_research_questionnaire--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,23 +515,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>demographics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your age?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please enter your age</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>demographics</t>
+          <t>product_use</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>demographics</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How long have you been using our product?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select one of the following options</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,20 +569,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>product_ranking</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>contact information</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>How do you rate our current product offerings?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select one of the following options</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,15 +601,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>market_trends</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>contact information</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How much do you know about market trends in the industry?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>This is a text field for you to enter any relevant information</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,15 +628,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>product_preferences</t>
+          <t>recent_purchase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>product preferences</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Have you recently purchased a similar product?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select one of the following options</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>product_preferences</t>
+          <t>product_attributes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>product preferences</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Which product attributes are most important to you?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select all that apply</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>market_trends</t>
+          <t>customer_service</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>market trends</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>How do you rate our customer service?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select one of the following options</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>market_trends</t>
+          <t>competitors</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>market trends</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Who are the top 3 competitors in the market?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please enter the names of the top 3 competitors separated by commas</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>product_attributes</t>
+          <t>purchasing_factors</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>product attributes</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What are the key factors that influence your purchasing decisions?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please enter any relevant information in this text field</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>product_attributes</t>
+          <t>product_usage</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>product attributes</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>How often do you use our product?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select one of the following options</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>competitive_analysis</t>
+          <t>product_impressions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>competitive analysis</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What are your impressions of our product?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please enter your impressions in this text field</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,20 +812,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>competitive_analysis</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>competitive analysis</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Do you have any feedback or suggestions for our company?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please enter any feedback or suggestions you may have</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -799,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,238 +875,425 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>demographics_choices</t>
+          <t>product_use_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>less_than_1_month</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Less than 1 month</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>demographics_choices</t>
+          <t>product_use_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>1-3_months</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1-3 months</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>product_preferences_choices</t>
+          <t>product_use_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>6-12_months</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>6-12 months</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>product_preferences_choices</t>
+          <t>product_use_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>product_preferences_choices</t>
+          <t>product_use_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2-5 years</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>product_preferences_choices</t>
+          <t>product_use_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>more_than_5_years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>More than 5 years</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>product_attributes_choices</t>
+          <t>product_ranking_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>1_(poor)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1 (Poor)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>product_attributes_choices</t>
+          <t>product_ranking_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>2_(fair)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2 (Fair)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>product_attributes_choices</t>
+          <t>product_ranking_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>3_(good)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>3 (Good)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>product_attributes_choices</t>
+          <t>product_ranking_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>4_(excellent)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>4 (Excellent)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>competitive_analysis_choices</t>
+          <t>recent_purchase_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>competitive_analysis_choices</t>
+          <t>recent_purchase_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>competitive_analysis_choices</t>
+          <t>product_attributes_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>price</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Price</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>competitive_analysis_choices</t>
+          <t>product_attributes_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>product_attributes_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>performance</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>product_attributes_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>product_attributes_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>customer_service_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1_(poor)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1 (Poor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>customer_service_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2_(fair)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2 (Fair)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>customer_service_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3_(good)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3 (Good)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>customer_service_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4_(excellent)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>4 (Excellent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>product_usage_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>product_usage_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>product_usage_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>frequently</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Frequently</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>product_usage_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>almost_daily</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Almost Daily</t>
         </is>
       </c>
     </row>
